--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -470,6 +470,35 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:drugNumber</t>
+  </si>
+  <si>
+    <t>drugNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_DrugNumber}
+</t>
+  </si>
+  <si>
+    <t>薬剤番号</t>
+  </si>
+  <si>
+    <t>薬剤番号を表現する拡張</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -499,9 +528,6 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
@@ -533,22 +559,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:rpNumber.id</t>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -570,7 +596,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.extension</t>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -588,7 +614,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.use</t>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -621,7 +647,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.type</t>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -658,16 +684,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.system</t>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -676,7 +702,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -688,19 +714,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.value</t>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -712,7 +738,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.period</t>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -737,7 +763,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.assigner</t>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -763,117 +789,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp</t>
-  </si>
-  <si>
-    <t>orderInRp</t>
-  </si>
-  <si>
-    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
-  </si>
-  <si>
-    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
-  </si>
-  <si>
-    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.use</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.type</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.system</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
-  </si>
-  <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.value</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番</t>
-  </si>
-  <si>
-    <t>剤グループ内連番。</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.period</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:orderInRp.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1840,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO74"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -3060,43 +2975,41 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3144,7 +3057,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3153,7 +3066,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3162,7 +3075,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3176,43 +3089,43 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3249,17 +3162,19 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AC12" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3271,19 +3186,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3291,46 +3206,46 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -3378,7 +3293,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3390,19 +3305,19 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3410,10 +3325,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3424,7 +3339,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3436,15 +3351,17 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3481,43 +3398,41 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3525,14 +3440,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3551,16 +3468,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3598,19 +3515,19 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3622,19 +3539,19 @@
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3642,10 +3559,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3662,26 +3579,22 @@
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3705,13 +3618,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3729,7 +3642,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3741,13 +3654,13 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3756,26 +3669,26 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3784,23 +3697,21 @@
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3824,49 +3735,49 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3875,15 +3786,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3891,7 +3802,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3900,32 +3811,32 @@
         <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3943,13 +3854,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3967,7 +3878,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3985,7 +3896,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3994,15 +3905,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>215</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4010,7 +3921,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -4025,18 +3936,20 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4060,13 +3973,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4084,7 +3997,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4102,7 +4015,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4111,15 +4024,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4127,7 +4040,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4142,22 +4055,26 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>79</v>
@@ -4199,7 +4116,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4217,7 +4134,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4226,15 +4143,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4242,7 +4159,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4257,16 +4174,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4316,7 +4233,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4334,7 +4251,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4343,19 +4260,17 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4364,7 +4279,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4373,20 +4288,18 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4435,13 +4348,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4450,27 +4363,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4490,18 +4403,20 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4550,7 +4465,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4562,13 +4477,13 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4577,19 +4492,19 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4608,17 +4523,15 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4655,19 +4568,19 @@
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4679,13 +4592,13 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4699,10 +4612,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4710,7 +4623,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -4728,17 +4641,15 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4762,13 +4673,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4786,10 +4697,10 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>89</v>
@@ -4801,27 +4712,27 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4841,23 +4752,19 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4881,13 +4788,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4905,7 +4812,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4920,10 +4827,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4932,15 +4839,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4948,7 +4855,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4960,29 +4867,27 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -5000,13 +4905,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5024,7 +4929,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5042,7 +4947,7 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5051,15 +4956,15 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5082,16 +4987,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5117,13 +5022,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5141,10 +5046,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>89</v>
@@ -5156,27 +5061,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>223</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>225</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5184,7 +5089,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5199,15 +5104,17 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5256,7 +5163,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5271,27 +5178,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5311,19 +5218,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5373,7 +5280,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5388,10 +5295,10 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5400,28 +5307,26 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5433,16 +5338,16 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>156</v>
+        <v>308</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5492,7 +5397,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5507,16 +5412,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5524,10 +5429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5538,7 +5443,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5550,13 +5455,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5607,25 +5512,25 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5639,21 +5544,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5665,17 +5570,15 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5712,37 +5615,37 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5756,46 +5659,44 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5819,49 +5720,49 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5870,50 +5771,50 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5938,13 +5839,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5962,25 +5863,25 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>204</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -5989,15 +5890,15 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6005,7 +5906,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -6017,29 +5918,27 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>79</v>
@@ -6057,13 +5956,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6081,7 +5980,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>213</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6099,7 +5998,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>214</v>
+        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -6108,15 +6007,15 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>217</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6136,20 +6035,18 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>172</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6198,10 +6095,10 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>221</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6213,10 +6110,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>222</v>
+        <v>338</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6225,15 +6122,15 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>223</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6253,18 +6150,20 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>227</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6313,7 +6212,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>229</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6331,7 +6230,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>230</v>
+        <v>343</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -6340,15 +6239,15 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>233</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6359,7 +6258,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6368,19 +6267,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>235</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>236</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>237</v>
+        <v>348</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6430,13 +6329,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>238</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6445,27 +6344,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>239</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>240</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6476,7 +6375,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6488,15 +6387,17 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>279</v>
+        <v>204</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6521,13 +6422,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6545,13 +6446,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6560,27 +6461,27 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6597,22 +6498,22 @@
         <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>363</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>285</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6638,13 +6539,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6662,42 +6563,42 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>291</v>
+        <v>368</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6720,15 +6621,17 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6753,13 +6656,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6777,7 +6680,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6786,16 +6689,16 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>367</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>368</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6804,15 +6707,15 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6832,20 +6735,18 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>196</v>
+        <v>374</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>375</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6870,13 +6771,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6894,7 +6795,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6912,24 +6813,24 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6949,20 +6850,18 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>196</v>
+        <v>374</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6987,13 +6886,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7011,10 +6910,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7026,27 +6925,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>320</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7054,7 +6953,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7066,19 +6965,19 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>323</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>324</v>
+        <v>386</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7128,7 +7027,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7143,27 +7042,27 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>329</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7174,7 +7073,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7186,16 +7085,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7245,13 +7144,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7260,16 +7159,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7277,10 +7176,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7303,16 +7202,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7362,7 +7261,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7377,27 +7276,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7420,15 +7319,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7477,7 +7378,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7492,10 +7393,10 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7509,10 +7410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7535,13 +7436,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>173</v>
+        <v>410</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>174</v>
+        <v>411</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7592,7 +7493,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7604,19 +7505,19 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7624,21 +7525,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7650,17 +7551,15 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7709,25 +7608,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7741,14 +7640,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>350</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>351</v>
+        <v>157</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7761,26 +7660,24 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>352</v>
+        <v>187</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>353</v>
+        <v>188</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7828,7 +7725,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>354</v>
+        <v>190</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7846,7 +7743,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7860,43 +7757,45 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>358</v>
+        <v>161</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7921,13 +7820,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7945,25 +7844,25 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>361</v>
+        <v>132</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7977,10 +7876,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8003,13 +7902,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>363</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8060,7 +7959,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>89</v>
@@ -8075,10 +7974,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8092,10 +7991,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8118,17 +8017,15 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>369</v>
+        <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8153,13 +8050,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8177,7 +8074,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8195,24 +8092,24 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8235,17 +8132,15 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>374</v>
+        <v>204</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>375</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8270,13 +8165,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8294,7 +8189,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8309,27 +8204,27 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8340,7 +8235,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8352,16 +8247,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>196</v>
+        <v>437</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>385</v>
+        <v>296</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8387,13 +8282,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8411,13 +8306,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8429,35 +8324,35 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>389</v>
+        <v>441</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8469,16 +8364,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>392</v>
+        <v>444</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>393</v>
+        <v>445</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>394</v>
+        <v>446</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>395</v>
+        <v>447</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8528,25 +8423,25 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>396</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8555,15 +8450,15 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8574,7 +8469,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8586,16 +8481,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>392</v>
+        <v>450</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>395</v>
+        <v>453</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8645,25 +8540,25 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>396</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8672,1866 +8567,6 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO74" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -470,35 +470,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>MedicationDispense.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
-  </si>
-  <si>
-    <t>MedicationDispense.extension:drugNumber</t>
-  </si>
-  <si>
-    <t>drugNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_DrugNumber}
-</t>
-  </si>
-  <si>
-    <t>薬剤番号</t>
-  </si>
-  <si>
-    <t>薬剤番号を表現する拡張</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -528,6 +499,9 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
@@ -559,22 +533,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+    <t>MedicationDispense.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -596,7 +570,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+    <t>MedicationDispense.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -614,7 +588,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+    <t>MedicationDispense.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -647,7 +621,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+    <t>MedicationDispense.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -684,16 +658,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+    <t>MedicationDispense.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -702,7 +676,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -714,19 +688,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+    <t>MedicationDispense.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -738,7 +712,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+    <t>MedicationDispense.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -763,7 +737,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
+    <t>MedicationDispense.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -789,6 +763,117 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp</t>
+  </si>
+  <si>
+    <t>orderInRp</t>
+  </si>
+  <si>
+    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
+  </si>
+  <si>
+    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
+  </si>
+  <si>
+    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.use</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.type</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.system</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
+  </si>
+  <si>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.value</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番</t>
+  </si>
+  <si>
+    <t>剤グループ内連番。</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.period</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:orderInRp.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1755,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -2975,41 +3060,43 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3057,7 +3144,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3066,7 +3153,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3075,7 +3162,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3089,23 +3176,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>79</v>
@@ -3117,15 +3202,17 @@
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3162,19 +3249,17 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3186,19 +3271,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3206,46 +3291,46 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -3293,7 +3378,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3305,19 +3390,19 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3325,10 +3410,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3339,7 +3424,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3351,17 +3436,15 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3398,41 +3481,43 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3440,16 +3525,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3468,16 +3551,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3515,19 +3598,19 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3539,19 +3622,19 @@
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3559,10 +3642,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3579,22 +3662,26 @@
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3618,13 +3705,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3642,7 +3729,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3654,13 +3741,13 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3669,26 +3756,26 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3697,21 +3784,23 @@
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3735,49 +3824,49 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3786,15 +3875,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3802,7 +3891,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3811,32 +3900,32 @@
         <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3854,13 +3943,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3878,7 +3967,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3896,7 +3985,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3905,15 +3994,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>132</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3921,7 +4010,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3936,20 +4025,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -3973,13 +4060,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3997,7 +4084,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4015,7 +4102,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4024,15 +4111,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4040,7 +4127,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4055,26 +4142,22 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>79</v>
@@ -4116,7 +4199,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4134,7 +4217,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4143,15 +4226,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4159,7 +4242,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4174,16 +4257,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4233,7 +4316,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4251,7 +4334,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4260,17 +4343,19 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4279,7 +4364,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4288,18 +4373,20 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4348,13 +4435,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4363,27 +4450,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4403,20 +4490,18 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4465,7 +4550,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4477,13 +4562,13 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4492,19 +4577,19 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4523,15 +4608,17 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>179</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4568,19 +4655,19 @@
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>182</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4592,13 +4679,13 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4612,10 +4699,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4623,7 +4710,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -4641,15 +4728,17 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4673,13 +4762,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>259</v>
+        <v>190</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4697,10 +4786,10 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>89</v>
@@ -4712,27 +4801,27 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4752,19 +4841,23 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>196</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>197</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4788,13 +4881,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>270</v>
+        <v>202</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4812,7 +4905,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4827,10 +4920,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4839,15 +4932,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4855,7 +4948,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4867,27 +4960,29 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -4905,13 +5000,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4929,7 +5024,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4947,7 +5042,7 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4956,15 +5051,15 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4987,16 +5082,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5022,13 +5117,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5046,10 +5141,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>89</v>
@@ -5061,27 +5156,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>222</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5089,7 +5184,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5104,17 +5199,15 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5163,7 +5256,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5178,27 +5271,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5218,19 +5311,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5280,7 +5373,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5295,10 +5388,10 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5307,26 +5400,28 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5338,16 +5433,16 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>156</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5397,7 +5492,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5412,16 +5507,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>162</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>163</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5429,10 +5524,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5443,7 +5538,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5455,13 +5550,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>173</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5512,25 +5607,25 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>318</v>
+        <v>176</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5544,21 +5639,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5570,15 +5665,17 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5615,37 +5712,37 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5659,44 +5756,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5720,13 +5819,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5744,25 +5843,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5771,50 +5870,50 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>195</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>197</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>198</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5839,13 +5938,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5863,25 +5962,25 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>204</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -5890,15 +5989,15 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5906,7 +6005,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -5918,27 +6017,29 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>211</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>79</v>
@@ -5956,13 +6057,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5980,7 +6081,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>213</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5998,7 +6099,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -6007,15 +6108,15 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>217</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6035,18 +6136,20 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6095,10 +6198,10 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>221</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6110,10 +6213,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>338</v>
+        <v>222</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6122,15 +6225,15 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>225</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6150,20 +6253,18 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>226</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>227</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6212,7 +6313,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>229</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6230,7 +6331,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>230</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -6239,15 +6340,15 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6258,7 +6359,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6267,19 +6368,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>236</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
+        <v>237</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6329,13 +6430,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6344,27 +6445,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>239</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6375,7 +6476,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6387,17 +6488,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>204</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6422,13 +6521,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6446,13 +6545,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6461,27 +6560,27 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6498,22 +6597,22 @@
         <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>363</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>366</v>
+        <v>287</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6539,13 +6638,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6563,42 +6662,42 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>367</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6621,17 +6720,15 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>363</v>
+        <v>295</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6656,13 +6753,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6680,7 +6777,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6689,16 +6786,16 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>367</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6707,15 +6804,15 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6735,18 +6832,20 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>374</v>
+        <v>196</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>375</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6771,13 +6870,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6795,7 +6894,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6813,24 +6912,24 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6850,18 +6949,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>374</v>
+        <v>196</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6886,13 +6987,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -6910,10 +7011,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6925,27 +7026,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>382</v>
+        <v>316</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>317</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>377</v>
+        <v>319</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>378</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6953,7 +7054,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -6965,19 +7066,19 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>323</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>324</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7027,7 +7128,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7042,27 +7143,27 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>389</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7073,7 +7174,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7085,16 +7186,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>391</v>
+        <v>331</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
+        <v>333</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7144,13 +7245,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7159,16 +7260,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7176,10 +7277,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7202,16 +7303,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>337</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>399</v>
+        <v>339</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7261,7 +7362,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7276,27 +7377,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>340</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7319,17 +7420,15 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7378,7 +7477,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7393,10 +7492,10 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7410,10 +7509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7436,13 +7535,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>410</v>
+        <v>173</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>411</v>
+        <v>174</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7493,7 +7592,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7505,19 +7604,19 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>412</v>
+        <v>176</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7525,21 +7624,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7551,15 +7650,17 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7608,25 +7709,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7640,14 +7741,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>157</v>
+        <v>351</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7660,24 +7761,26 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7725,7 +7828,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>190</v>
+        <v>354</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7743,7 +7846,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7757,45 +7860,43 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>161</v>
+        <v>358</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7820,13 +7921,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7844,25 +7945,25 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>132</v>
+        <v>361</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7876,10 +7977,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7902,13 +8003,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7959,7 +8060,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>89</v>
@@ -7974,10 +8075,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7991,10 +8092,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8017,15 +8118,17 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>204</v>
+        <v>369</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8050,13 +8153,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8074,7 +8177,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8092,24 +8195,24 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8132,15 +8235,17 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>204</v>
+        <v>374</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>375</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8165,13 +8270,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8189,7 +8294,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8204,27 +8309,27 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>435</v>
+        <v>380</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8235,7 +8340,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8247,16 +8352,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>438</v>
+        <v>383</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>439</v>
+        <v>384</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8282,13 +8387,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8306,13 +8411,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8324,35 +8429,35 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>440</v>
+        <v>388</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>441</v>
+        <v>389</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8364,16 +8469,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>445</v>
+        <v>393</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>446</v>
+        <v>394</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8423,25 +8528,25 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>396</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8450,15 +8555,15 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8469,7 +8574,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8481,16 +8586,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>450</v>
+        <v>392</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>453</v>
+        <v>395</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8540,33 +8645,1893 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
+      <c r="H71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AK71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -667,7 +667,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -676,7 +676,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -801,7 +801,7 @@
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.value</t>
@@ -855,10 +855,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:orderInRp.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -594,22 +594,22 @@
     <t>MedicationDispense.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -631,22 +631,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -670,10 +670,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -725,7 +725,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -750,10 +750,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -777,7 +777,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.id</t>
@@ -795,7 +795,7 @@
     <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -810,10 +810,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.period</t>
@@ -1250,7 +1250,7 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1514,7 +1514,7 @@
 DetectedIssue リソースへの参照。</t>
   </si>
   <si>
-    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られた手順に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
+    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られたプロシジャー（処置等）に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=ALRT,moodCode=EVN].value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -1250,14 +1250,13 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>CombinedMedicationDispense.SupplyEvent.quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -1267,6 +1266,15 @@
   </si>
   <si>
     <t>タイミングとして表される投薬量。すなわち、XX日分、XX回分などの数量。</t>
+  </si>
+  <si>
+    <t>effectiveUseTime</t>
+  </si>
+  <si>
+    <t>TQ1.6 Timing/Quantity Segment Service Duration.+Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
     <t>MedicationDispense.whenPrepared</t>
@@ -1374,7 +1382,10 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>患者が薬をどのように使用するか、または介護者が投与する / How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>投与または速度が行政期間全体で変化することを目的としている場合（例：用量処方の先細り）、さまざまな用量/レートを伝えるために投与量の指示の複数のインスタンスを提供する必要があります。@@ -1882,7 +1893,7 @@
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="94.375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8537,22 +8548,22 @@
         <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>398</v>
@@ -8654,16 +8665,16 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>396</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8672,15 +8683,15 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8703,13 +8714,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8760,7 +8771,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8778,24 +8789,24 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8818,13 +8829,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8875,7 +8886,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8890,27 +8901,27 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8936,10 +8947,10 @@
         <v>369</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>325</v>
@@ -8992,7 +9003,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9010,24 +9021,24 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9050,13 +9061,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>325</v>
@@ -9109,7 +9120,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9127,13 +9138,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9141,10 +9152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9167,16 +9178,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9226,7 +9237,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9241,10 +9252,10 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9253,15 +9264,15 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9284,16 +9295,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9343,7 +9354,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9361,7 +9372,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9375,10 +9386,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9404,10 +9415,10 @@
         <v>343</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9458,7 +9469,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9476,13 +9487,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9490,10 +9501,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9605,10 +9616,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9722,10 +9733,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9841,10 +9852,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9867,13 +9878,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9924,7 +9935,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -9942,7 +9953,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -9956,10 +9967,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9985,10 +9996,10 @@
         <v>196</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10018,28 +10029,28 @@
         <v>298</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10063,18 +10074,18 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10100,10 +10111,10 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10133,28 +10144,28 @@
         <v>298</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10172,13 +10183,13 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10186,10 +10197,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10212,13 +10223,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>325</v>
@@ -10271,7 +10282,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10289,13 +10300,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10303,14 +10314,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10329,16 +10340,16 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10388,7 +10399,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10406,7 +10417,7 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10420,10 +10431,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10446,16 +10457,16 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10505,7 +10516,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10523,7 +10534,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -1273,7 +1273,7 @@
   <si>
     <t>TQ1.6 Timing/Quantity Segment Service Duration. Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”-From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (Quantity (NM) ^ Units (CWE)), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^ For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -1854,17 +1854,17 @@
   <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1873,26 +1873,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="197.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -1149,10 +1149,10 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人 / Individual who was performing</t>
-  </si>
-  <si>
-    <t>アクションを実行したデバイス、開業医など。俳優は薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -743,7 +743,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -929,7 +929,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -944,7 +944,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -968,7 +968,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -1062,7 +1062,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1136,7 +1136,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1514,7 +1514,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1534,7 +1534,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -1470,16 +1470,13 @@
     <t>MedicationDispense.substitution.reason</t>
   </si>
   <si>
-    <t>置換が実施された理由</t>
-  </si>
-  <si>
-    <t>治療継続性確保のため、FP:処方方針、 OS: 在庫欠品、  RR:代替えを義務付けまたは禁止する規制要件に従った</t>
-  </si>
-  <si>
-    <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>置換が実施された（あるいは、されなかった）理由</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】置換が実施された、あるいは実施されなかった理由を示す。令和6年保険改訂により、処方箋上で長期収載医薬品の変更不可が指定されている場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1879,7 +1876,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.2890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -10141,13 +10138,11 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Y71" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y71" s="2"/>
+      <c r="Z71" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10183,13 +10178,13 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10197,10 +10192,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10223,13 +10218,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>325</v>
@@ -10282,7 +10277,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10300,13 +10295,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10314,14 +10309,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10340,16 +10335,16 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10399,7 +10394,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10417,7 +10412,7 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10431,10 +10426,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10457,16 +10452,16 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10516,7 +10511,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10534,7 +10529,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -1214,7 +1214,7 @@
     <t>実行される調剤イベントのタイプを示す。たとえば、トライアルフィル、トライアルの完了、部分フィル、緊急フィル、サンプルなどである。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -511,7 +511,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1363,7 +1363,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
